--- a/Reports/Recalculation/HOT_autoRecalc/HOT_autoRecalc.xlsx
+++ b/Reports/Recalculation/HOT_autoRecalc/HOT_autoRecalc.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\Recalculation\HOT_autoRecalc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB6F31D-4716-415F-997C-40785C1CE953}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600"/>
+    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -183,9 +189,6 @@
     <t>ИТОГО:</t>
   </si>
   <si>
-    <t>Ведущий специалист по ПСХ                                                            Д.С.Карпенко</t>
-  </si>
-  <si>
     <r>
       <t>Общая площадь дома, м</t>
     </r>
@@ -314,9 +317,6 @@
     <t>$t1['calculate'] == '1' ? "=J$R/B$R"  : ""</t>
   </si>
   <si>
-    <t>"Корректировка потребления тепловой энергии согласно показаний ОДПУ по жилому дому, расположенному в пгт Бачатский, ".$t2['addres_house'].", за период с 01.01.2023г по 31.12.2023г."</t>
-  </si>
-  <si>
     <t>"=L$R-I$R"</t>
   </si>
   <si>
@@ -330,17 +330,23 @@
   </si>
   <si>
     <t>$t1['name_JEU']</t>
+  </si>
+  <si>
+    <t>"Корректировка потребления тепловой энергии согласно показаний ОДПУ по жилому дому, расположенному в пгт Бачатский, ".$t2['addres_house'].", за период с 01.01.2025г по 31.12.2025г."</t>
+  </si>
+  <si>
+    <t>Ведущий специалист по ПСХ                                                            Е.В. Долгова</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,28 +588,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -616,6 +622,14 @@
       <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -662,7 +676,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -694,9 +708,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -728,6 +760,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -903,12 +953,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="3" customWidth="1"/>
     <col min="2" max="8" width="13.28515625" style="3" customWidth="1"/>
@@ -922,7 +972,7 @@
     <col min="32" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="19.5">
+    <row r="1" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -934,11 +984,11 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
       <c r="O1" s="34"/>
       <c r="P1" s="20"/>
       <c r="Q1" s="31"/>
@@ -959,7 +1009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="19.5">
+    <row r="2" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -971,11 +1021,11 @@
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
       <c r="O2" s="33"/>
       <c r="P2" s="19"/>
       <c r="Q2" s="30"/>
@@ -986,7 +1036,7 @@
       <c r="V2" s="5"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" spans="1:29" ht="19.5">
+    <row r="3" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -998,11 +1048,11 @@
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
       <c r="O3" s="33"/>
       <c r="P3" s="19"/>
       <c r="Q3" s="30"/>
@@ -1013,7 +1063,7 @@
       <c r="V3" s="5"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" spans="1:29" ht="19.5">
+    <row r="4" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1025,11 +1075,11 @@
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="39" t="s">
+      <c r="L4" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
       <c r="O4" s="33"/>
       <c r="P4" s="19"/>
       <c r="Q4" s="30"/>
@@ -1040,7 +1090,7 @@
       <c r="V4" s="5"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" spans="1:29" ht="19.5">
+    <row r="5" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1052,11 +1102,11 @@
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
-      <c r="L5" s="39" t="s">
+      <c r="L5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
       <c r="O5" s="33"/>
       <c r="P5" s="19"/>
       <c r="Q5" s="30"/>
@@ -1067,7 +1117,7 @@
       <c r="V5" s="5"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1092,23 +1142,23 @@
       <c r="V6" s="5"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" spans="1:29" ht="55.5" customHeight="1">
-      <c r="A7" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
+    <row r="7" spans="1:29" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
       <c r="O7" s="35"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="32"/>
@@ -1119,7 +1169,7 @@
       <c r="V7" s="5"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1144,46 +1194,46 @@
       <c r="V8" s="5"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" spans="1:29">
-      <c r="A9" s="38" t="s">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A9" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="D9" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38" t="s">
+      <c r="H9" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="42"/>
+      <c r="O9" s="38"/>
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="R9" s="15"/>
@@ -1193,27 +1243,27 @@
       <c r="V9" s="5"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" spans="1:29" ht="93" customHeight="1">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
+    <row r="10" spans="1:29" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
       <c r="D10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="F10" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
       <c r="O10" s="23" t="s">
         <v>52</v>
       </c>
@@ -1232,7 +1282,7 @@
       <c r="V10" s="5"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>18</v>
       </c>
@@ -1261,23 +1311,23 @@
         <v>51</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="43"/>
+      <c r="O11" s="39"/>
       <c r="P11" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="17"/>
@@ -1296,7 +1346,7 @@
       </c>
       <c r="X11" s="7"/>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>53</v>
       </c>
@@ -1340,13 +1390,13 @@
         <v>48</v>
       </c>
       <c r="O12" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P12" s="36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R12" s="17"/>
       <c r="S12" s="4"/>
@@ -1379,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="18.75" customHeight="1">
+    <row r="13" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="T13" s="8" t="s">
         <v>3</v>
       </c>
@@ -1395,12 +1445,12 @@
       <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="18" customHeight="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R16" s="3" t="s">
         <v>25</v>
       </c>
@@ -1411,7 +1461,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="20:30" ht="18" customHeight="1">
+    <row r="17" spans="20:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="T17" s="5" t="s">
         <v>4</v>
       </c>
@@ -1422,8 +1472,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="20:30" ht="18.75" customHeight="1"/>
-    <row r="24" spans="20:30">
+    <row r="18" spans="20:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
       <c r="V24" s="10"/>
@@ -1436,7 +1486,7 @@
       <c r="AC24" s="10"/>
       <c r="AD24" s="10"/>
     </row>
-    <row r="25" spans="20:30">
+    <row r="25" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9"/>
@@ -1449,7 +1499,7 @@
       <c r="AC25" s="10"/>
       <c r="AD25" s="10"/>
     </row>
-    <row r="26" spans="20:30">
+    <row r="26" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
       <c r="V26" s="9"/>
@@ -1462,7 +1512,7 @@
       <c r="AC26" s="9"/>
       <c r="AD26" s="10"/>
     </row>
-    <row r="27" spans="20:30">
+    <row r="27" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
@@ -1475,7 +1525,7 @@
       <c r="AC27" s="10"/>
       <c r="AD27" s="10"/>
     </row>
-    <row r="28" spans="20:30">
+    <row r="28" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
       <c r="V28" s="10"/>
@@ -1488,7 +1538,7 @@
       <c r="AC28" s="10"/>
       <c r="AD28" s="10"/>
     </row>
-    <row r="29" spans="20:30">
+    <row r="29" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
@@ -1501,7 +1551,7 @@
       <c r="AC29" s="9"/>
       <c r="AD29" s="10"/>
     </row>
-    <row r="30" spans="20:30">
+    <row r="30" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
       <c r="V30" s="9"/>
@@ -1514,7 +1564,7 @@
       <c r="AC30" s="10"/>
       <c r="AD30" s="10"/>
     </row>
-    <row r="31" spans="20:30">
+    <row r="31" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
@@ -1527,7 +1577,7 @@
       <c r="AC31" s="10"/>
       <c r="AD31" s="10"/>
     </row>
-    <row r="32" spans="20:30">
+    <row r="32" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
@@ -1540,7 +1590,7 @@
       <c r="AC32" s="10"/>
       <c r="AD32" s="10"/>
     </row>
-    <row r="33" spans="20:30">
+    <row r="33" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
@@ -1553,7 +1603,7 @@
       <c r="AC33" s="10"/>
       <c r="AD33" s="10"/>
     </row>
-    <row r="34" spans="20:30">
+    <row r="34" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
@@ -1566,12 +1616,14 @@
       <c r="AC34" s="10"/>
       <c r="AD34" s="10"/>
     </row>
-    <row r="41" spans="20:30">
+    <row r="41" spans="20:30" x14ac:dyDescent="0.3">
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="A9:A10"/>
@@ -1588,8 +1640,6 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.39370078740157483" bottom="0.78740157480314965" header="0" footer="0"/>
@@ -1601,18 +1651,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
